--- a/Excel Files - Direct Import/Excel Files - Direct Import/Surgery.xlsx
+++ b/Excel Files - Direct Import/Excel Files - Direct Import/Surgery.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faisa\OneDrive\Documents\Hospital_CAI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/76c9c0d5115733c1/Documents/Data Analysis/Power BI/Hospital_Data_Analysis/Excel Files - Direct Import/Excel Files - Direct Import/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DDC832D-03D3-4E1D-AD1A-EC22C7EC9005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{4DDC832D-03D3-4E1D-AD1A-EC22C7EC9005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C524B479-4D6D-49A6-88A2-B75B08B454CE}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{90F7F0BD-DE89-4433-B1CF-7611AB4BAB1F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{90F7F0BD-DE89-4433-B1CF-7611AB4BAB1F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -713,7 +713,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -750,7 +750,9 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{7DB7A522-1414-4231-A40D-0B6DF2273C87}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
